--- a/data/trans_bre/PCS12_SP_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/PCS12_SP_R2-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12)</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,72; 17,31</t>
+          <t>9,65; 17,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,95; 13,09</t>
+          <t>5,12; 12,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,14; 16,4</t>
+          <t>7,29; 16,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,29; 16,39</t>
+          <t>7,5; 16,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,88; 29,03</t>
+          <t>14,75; 28,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,31; 21,07</t>
+          <t>7,49; 20,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,67; 27,84</t>
+          <t>11,69; 27,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,15; 25,39</t>
+          <t>10,4; 25,72</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,17; 14,73</t>
+          <t>8,11; 14,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 9,86</t>
+          <t>3,02; 9,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,88</t>
+          <t>1,59; 8,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 14,96</t>
+          <t>-14,93; 13,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,89; 46,11</t>
+          <t>22,65; 46,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,55; 27,87</t>
+          <t>7,68; 27,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,66; 23,97</t>
+          <t>4,43; 24,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,98; 34,16</t>
+          <t>-26,72; 32,36</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,43; 17,81</t>
+          <t>5,38; 18,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 14,54</t>
+          <t>1,22; 14,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 13,37</t>
+          <t>1,91; 13,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 3,75</t>
+          <t>-6,51; 4,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,56; 61,6</t>
+          <t>15,62; 63,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 54,64</t>
+          <t>3,8; 54,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,44; 58,24</t>
+          <t>6,8; 61,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 9,09</t>
+          <t>-14,57; 10,99</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,98; 16,81</t>
+          <t>11,92; 16,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,88; 12,77</t>
+          <t>7,86; 12,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 11,19</t>
+          <t>6,25; 11,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 11,67</t>
+          <t>-5,56; 12,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,35; 40,73</t>
+          <t>27,33; 41,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,31; 29,87</t>
+          <t>17,23; 29,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,04; 29,96</t>
+          <t>15,51; 29,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 24,25</t>
+          <t>-10,45; 26,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/PCS12_SP_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/PCS12_SP_R2-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,93</t>
+          <t>13,38</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,65; 17,26</t>
+          <t>9,61; 17,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,12; 12,95</t>
+          <t>5,0; 13,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,29; 16,23</t>
+          <t>6,75; 15,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,5; 16,65</t>
+          <t>8,88; 18,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,75; 28,62</t>
+          <t>14,86; 29,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,49; 20,96</t>
+          <t>7,28; 20,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,69; 27,67</t>
+          <t>10,53; 27,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,4; 25,72</t>
+          <t>12,98; 29,57</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,37</t>
+          <t>5,32</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,11; 14,95</t>
+          <t>8,17; 15,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 9,8</t>
+          <t>3,28; 9,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 8,01</t>
+          <t>1,75; 7,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 13,85</t>
+          <t>2,21; 8,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,65; 46,4</t>
+          <t>23,05; 46,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,68; 27,36</t>
+          <t>8,32; 27,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 24,77</t>
+          <t>5,04; 23,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,72; 32,36</t>
+          <t>5,12; 21,14</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,65</t>
+          <t>-0,27</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-3,88%</t>
+          <t>-0,64%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,38; 18,36</t>
+          <t>4,84; 17,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 14,09</t>
+          <t>1,95; 14,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 13,71</t>
+          <t>2,04; 13,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 4,24</t>
+          <t>-5,27; 5,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,62; 63,97</t>
+          <t>12,88; 58,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 54,11</t>
+          <t>5,84; 55,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,8; 61,09</t>
+          <t>7,04; 59,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 10,99</t>
+          <t>-11,58; 13,14</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,77</t>
+          <t>7,31</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,92; 16,96</t>
+          <t>12,04; 16,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 12,7</t>
+          <t>7,76; 12,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 11,11</t>
+          <t>6,33; 11,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 12,42</t>
+          <t>4,88; 9,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,33; 41,75</t>
+          <t>27,23; 41,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,23; 29,88</t>
+          <t>17,32; 30,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,51; 29,33</t>
+          <t>15,6; 30,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 26,14</t>
+          <t>10,39; 21,84</t>
         </is>
       </c>
     </row>
